--- a/config/配置_万润_EMS.xlsx
+++ b/config/配置_万润_EMS.xlsx
@@ -511,16 +511,16 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/pcs/PCS_英博_协控.xlsx</t>
+    <t>./config/pcs/PCS_英博_大机.xlsx</t>
   </si>
   <si>
     <t>192.168.0.1</t>
   </si>
   <si>
+    <t>./config/bms/BAU_协能.xlsx</t>
+  </si>
+  <si>
     <t>192.168.0.2</t>
-  </si>
-  <si>
-    <t>./config/bms/BAU_协能.xlsx</t>
   </si>
   <si>
     <t>./config/bms/BCU_协能.xlsx</t>
@@ -1263,7 +1263,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,15 +1280,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1722,401 +1713,401 @@
     <col min="8" max="16384" width="9.03100775193798" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" spans="1:7">
-      <c r="A1" s="11" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:7">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="12" customFormat="1" spans="1:7">
-      <c r="A2" s="12" t="s">
+    <row r="2" s="9" customFormat="1" spans="1:7">
+      <c r="A2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="12" t="b">
+      <c r="F2" s="9" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="13" customFormat="1" spans="1:7">
-      <c r="A3" s="13" t="s">
+    <row r="3" s="10" customFormat="1" spans="1:7">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="13" t="b">
+      <c r="F3" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1" spans="1:7">
-      <c r="B4" s="13" t="s">
+    <row r="4" s="10" customFormat="1" spans="1:7">
+      <c r="B4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="10">
         <v>9091</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="14" customFormat="1" spans="1:7">
-      <c r="A5" s="14" t="s">
+    <row r="5" s="11" customFormat="1" spans="1:7">
+      <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="14" t="b">
+      <c r="F5" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" s="15" customFormat="1" spans="1:7">
-      <c r="A6" s="15" t="s">
+    <row r="6" s="12" customFormat="1" spans="1:7">
+      <c r="A6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="15" t="b">
+      <c r="F6" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" s="15" customFormat="1" spans="1:7">
-      <c r="B7" s="15" t="s">
+    <row r="7" s="12" customFormat="1" spans="1:7">
+      <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="12">
         <v>9092</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" s="15" customFormat="1" spans="1:7">
-      <c r="B8" s="15" t="s">
+    <row r="8" s="12" customFormat="1" spans="1:7">
+      <c r="B8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" s="16" customFormat="1" spans="1:7">
-      <c r="A9" s="16" t="s">
+    <row r="9" s="13" customFormat="1" spans="1:7">
+      <c r="A9" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="20" t="b">
+      <c r="F9" s="17" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" s="16" customFormat="1" spans="1:7">
-      <c r="B10" s="16" t="s">
+    <row r="10" s="13" customFormat="1" spans="1:7">
+      <c r="B10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <v>2404</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-    </row>
-    <row r="11" s="16" customFormat="1" spans="1:7">
-      <c r="B11" s="16" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+    </row>
+    <row r="11" s="13" customFormat="1" spans="1:7">
+      <c r="B11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-    </row>
-    <row r="12" s="16" customFormat="1" spans="1:7">
-      <c r="B12" s="16" t="s">
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" s="13" customFormat="1" spans="1:7">
+      <c r="B12" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-    </row>
-    <row r="13" s="16" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B13" s="16" t="s">
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+    </row>
+    <row r="13" s="13" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="16" t="b">
+      <c r="C13" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" s="16" customFormat="1" spans="1:7">
-      <c r="B14" s="16" t="s">
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+    </row>
+    <row r="14" s="13" customFormat="1" spans="1:7">
+      <c r="B14" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <v>30000</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" s="16" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B15" s="16" t="s">
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+    </row>
+    <row r="15" s="13" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="16" t="b">
+      <c r="C15" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" s="17" customFormat="1" spans="1:7">
-      <c r="A16" s="24" t="s">
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" s="14" customFormat="1" spans="1:7">
+      <c r="A16" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="25" t="b">
+      <c r="F16" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G16" s="22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" s="17" customFormat="1" spans="1:7">
-      <c r="A17" s="25"/>
-      <c r="B17" s="17" t="s">
+    <row r="17" s="14" customFormat="1" spans="1:7">
+      <c r="A17" s="22"/>
+      <c r="B17" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="14">
         <v>500</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-    </row>
-    <row r="18" s="17" customFormat="1" spans="1:7">
-      <c r="A18" s="25"/>
-      <c r="B18" s="17" t="s">
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+    </row>
+    <row r="18" s="14" customFormat="1" spans="1:7">
+      <c r="A18" s="22"/>
+      <c r="B18" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="14">
         <v>60000</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-    </row>
-    <row r="19" s="17" customFormat="1" spans="1:7">
-      <c r="A19" s="25"/>
-      <c r="B19" s="17" t="s">
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+    </row>
+    <row r="19" s="14" customFormat="1" spans="1:7">
+      <c r="A19" s="22"/>
+      <c r="B19" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="14">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-    </row>
-    <row r="20" s="17" customFormat="1" spans="1:7">
-      <c r="A20" s="25"/>
-      <c r="B20" s="17" t="s">
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+    </row>
+    <row r="20" s="14" customFormat="1" spans="1:7">
+      <c r="A20" s="22"/>
+      <c r="B20" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-    </row>
-    <row r="21" s="17" customFormat="1" ht="36.85" spans="1:7">
-      <c r="A21" s="25"/>
-      <c r="B21" s="17" t="s">
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+    </row>
+    <row r="21" s="14" customFormat="1" ht="36.85" spans="1:7">
+      <c r="A21" s="22"/>
+      <c r="B21" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="26" t="b">
+      <c r="C21" s="23" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-    </row>
-    <row r="22" s="18" customFormat="1" spans="1:7">
-      <c r="A22" s="18" t="s">
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+    </row>
+    <row r="22" s="15" customFormat="1" spans="1:7">
+      <c r="A22" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="18" t="b">
+      <c r="F22" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="15" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" s="19" customFormat="1" spans="1:7">
-      <c r="A23" s="19" t="s">
+    <row r="23" s="16" customFormat="1" spans="1:7">
+      <c r="A23" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F23" s="19" t="b">
+      <c r="F23" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="16" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" s="19" customFormat="1" spans="1:7">
-      <c r="B24" s="19" t="s">
+    <row r="24" s="16" customFormat="1" spans="1:7">
+      <c r="B24" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="16">
         <v>1883</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="16" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" s="19" customFormat="1" spans="1:7">
-      <c r="B25" s="19" t="s">
+    <row r="25" s="16" customFormat="1" spans="1:7">
+      <c r="B25" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" s="19" customFormat="1" spans="1:7">
-      <c r="B26" s="19" t="s">
+    <row r="26" s="16" customFormat="1" spans="1:7">
+      <c r="B26" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" s="19" customFormat="1" spans="1:7">
-      <c r="B27" s="19" t="s">
+    <row r="27" s="16" customFormat="1" spans="1:7">
+      <c r="B27" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="16" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" s="19" customFormat="1" spans="1:7">
-      <c r="B28" s="19" t="s">
+    <row r="28" s="16" customFormat="1" spans="1:7">
+      <c r="B28" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="16" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2730,17 +2721,17 @@
   <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4"/>
   <cols>
-    <col min="1" max="1" width="6.45736434108527" style="7" customWidth="1"/>
-    <col min="2" max="2" width="15.5968992248062" style="7" customWidth="1"/>
-    <col min="3" max="3" width="13.4573643410853" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.9302325581395" style="7" customWidth="1"/>
-    <col min="5" max="5" width="44.5348837209302" style="7" customWidth="1"/>
-    <col min="6" max="10" width="12.2015503875969" style="7" customWidth="1"/>
-    <col min="11" max="11" width="16.6666666666667" style="7" customWidth="1"/>
-    <col min="12" max="16" width="12.2015503875969" style="7" customWidth="1"/>
-    <col min="17" max="17" width="9.06976744186047" style="7"/>
-    <col min="18" max="18" width="15.2170542635659" style="7" customWidth="1"/>
-    <col min="19" max="16384" width="9.06976744186047" style="7"/>
+    <col min="1" max="1" width="6.45736434108527" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15.5968992248062" style="5" customWidth="1"/>
+    <col min="3" max="3" width="13.4573643410853" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.9302325581395" style="5" customWidth="1"/>
+    <col min="5" max="5" width="44.5348837209302" style="5" customWidth="1"/>
+    <col min="6" max="10" width="12.2015503875969" style="5" customWidth="1"/>
+    <col min="11" max="11" width="16.6666666666667" style="5" customWidth="1"/>
+    <col min="12" max="16" width="12.2015503875969" style="5" customWidth="1"/>
+    <col min="17" max="17" width="9.06976744186047" style="5"/>
+    <col min="18" max="18" width="15.2170542635659" style="5" customWidth="1"/>
+    <col min="19" max="16384" width="9.06976744186047" style="5"/>
   </cols>
   <sheetData>
     <row r="1" s="4" customFormat="1" spans="1:19">
@@ -2774,22 +2765,22 @@
       <c r="J1" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="4" t="s">
         <v>154</v>
       </c>
       <c r="Q1" s="4" t="s">
@@ -2803,16 +2794,16 @@
       </c>
     </row>
     <row r="2" s="5" customFormat="1" spans="1:19">
-      <c r="A2" s="7">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>157</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2845,20 +2836,20 @@
       </c>
     </row>
     <row r="3" s="5" customFormat="1" spans="1:19">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="7" t="s">
         <v>157</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F3" s="5">
         <v>2000</v>
@@ -2867,7 +2858,7 @@
         <v>2000</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I3" s="5">
         <v>502</v>
@@ -2876,21 +2867,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="6" customFormat="1" spans="1:19">
-      <c r="A4" s="7">
+    <row r="4" s="5" customFormat="1" spans="1:19">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>161</v>
+      <c r="E4" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="F4" s="5">
         <v>2000</v>
@@ -2899,7 +2890,7 @@
         <v>2000</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I4" s="5">
         <v>502</v>
@@ -2908,20 +2899,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="1" spans="1:19">
-      <c r="A5" s="7">
+    <row r="5" s="5" customFormat="1" spans="1:19">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F5" s="5">
@@ -2931,7 +2922,7 @@
         <v>2000</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I5" s="5">
         <v>502</v>
@@ -2940,20 +2931,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" spans="1:19">
-      <c r="A6" s="7">
+    <row r="6" s="5" customFormat="1" spans="1:19">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F6" s="5">
@@ -2963,7 +2954,7 @@
         <v>2000</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I6" s="5">
         <v>502</v>
@@ -2972,20 +2963,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" spans="1:19">
-      <c r="A7" s="7">
+    <row r="7" s="5" customFormat="1" spans="1:19">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F7" s="5">
@@ -2995,7 +2986,7 @@
         <v>2000</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I7" s="5">
         <v>502</v>
@@ -3004,20 +2995,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" spans="1:19">
-      <c r="A8" s="7">
+    <row r="8" s="5" customFormat="1" spans="1:19">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F8" s="5">
@@ -3027,7 +3018,7 @@
         <v>2000</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I8" s="5">
         <v>502</v>
@@ -3036,20 +3027,20 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" spans="1:19">
-      <c r="A9" s="7">
+    <row r="9" s="5" customFormat="1" spans="1:19">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F9" s="5">
@@ -3059,7 +3050,7 @@
         <v>2000</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I9" s="5">
         <v>502</v>
@@ -3068,20 +3059,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" spans="1:19">
-      <c r="A10" s="7">
+    <row r="10" s="5" customFormat="1" spans="1:19">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F10" s="5">
@@ -3091,7 +3082,7 @@
         <v>2000</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I10" s="5">
         <v>502</v>
@@ -3100,20 +3091,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" spans="1:19">
-      <c r="A11" s="7">
+    <row r="11" s="5" customFormat="1" spans="1:19">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F11" s="5">
@@ -3123,7 +3114,7 @@
         <v>2000</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I11" s="5">
         <v>502</v>
@@ -3132,20 +3123,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" spans="1:19">
-      <c r="A12" s="7">
+    <row r="12" s="5" customFormat="1" spans="1:19">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F12" s="5">
@@ -3155,7 +3146,7 @@
         <v>2000</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I12" s="5">
         <v>502</v>
@@ -3164,20 +3155,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" spans="1:19">
-      <c r="A13" s="7">
+    <row r="13" s="5" customFormat="1" spans="1:19">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F13" s="5">
@@ -3187,7 +3178,7 @@
         <v>2000</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I13" s="5">
         <v>502</v>
@@ -3196,20 +3187,20 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" s="6" customFormat="1" spans="1:19">
-      <c r="A14" s="7">
+    <row r="14" s="5" customFormat="1" spans="1:19">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F14" s="5">
@@ -3219,7 +3210,7 @@
         <v>2000</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I14" s="5">
         <v>502</v>
@@ -3228,20 +3219,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" s="6" customFormat="1" spans="1:19">
-      <c r="A15" s="7">
+    <row r="15" s="5" customFormat="1" spans="1:19">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>162</v>
       </c>
       <c r="F15" s="5">
@@ -3251,7 +3242,7 @@
         <v>2000</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I15" s="5">
         <v>502</v>

--- a/config/配置_万润_EMS.xlsx
+++ b/config/配置_万润_EMS.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24634" windowHeight="10697" activeTab="4"/>
+    <workbookView windowWidth="24685" windowHeight="11640" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="131">
   <si>
     <t>key</t>
   </si>
@@ -355,118 +355,13 @@
     <t>英博电气2.5MW</t>
   </si>
   <si>
-    <t>bau</t>
-  </si>
-  <si>
-    <t>BAU</t>
-  </si>
-  <si>
-    <t>协能BAU</t>
-  </si>
-  <si>
-    <t>bcu1</t>
-  </si>
-  <si>
-    <t>BCU</t>
-  </si>
-  <si>
-    <t>协能BCU</t>
-  </si>
-  <si>
-    <t>bcu2</t>
-  </si>
-  <si>
-    <t>bcu3</t>
-  </si>
-  <si>
-    <t>bcu4</t>
-  </si>
-  <si>
-    <t>bcu5</t>
-  </si>
-  <si>
-    <t>bcu6</t>
-  </si>
-  <si>
-    <t>bcu7</t>
-  </si>
-  <si>
-    <t>bcu8</t>
-  </si>
-  <si>
-    <t>bcu9</t>
-  </si>
-  <si>
-    <t>bcu10</t>
-  </si>
-  <si>
-    <t>bcu11</t>
-  </si>
-  <si>
-    <t>bcu12</t>
-  </si>
-  <si>
-    <t>10kv_meter1</t>
-  </si>
-  <si>
-    <t>KV_METER</t>
-  </si>
-  <si>
-    <t>高压侧10kV电表</t>
-  </si>
-  <si>
-    <t>10kv_meter2</t>
-  </si>
-  <si>
-    <t>meter1</t>
-  </si>
-  <si>
-    <t>METER</t>
-  </si>
-  <si>
-    <t>低压侧电表</t>
-  </si>
-  <si>
-    <t>meter2</t>
-  </si>
-  <si>
-    <t>meter3</t>
-  </si>
-  <si>
-    <t>meter4</t>
-  </si>
-  <si>
-    <t>meter5</t>
-  </si>
-  <si>
-    <t>meter6</t>
-  </si>
-  <si>
-    <t>meter7</t>
-  </si>
-  <si>
-    <t>meter8</t>
-  </si>
-  <si>
-    <t>meter9</t>
-  </si>
-  <si>
-    <t>meter10</t>
-  </si>
-  <si>
-    <t>meter11</t>
-  </si>
-  <si>
-    <t>meter12</t>
-  </si>
-  <si>
-    <t>meter13</t>
-  </si>
-  <si>
-    <t>meter14</t>
-  </si>
-  <si>
-    <t>meter15</t>
+    <t>crd</t>
+  </si>
+  <si>
+    <t>CRD</t>
+  </si>
+  <si>
+    <t>测控柜</t>
   </si>
   <si>
     <t>comType</t>
@@ -514,16 +409,16 @@
     <t>./config/pcs/PCS_英博_大机.xlsx</t>
   </si>
   <si>
-    <t>192.168.0.1</t>
-  </si>
-  <si>
-    <t>./config/bms/BAU_协能.xlsx</t>
-  </si>
-  <si>
-    <t>192.168.0.2</t>
-  </si>
-  <si>
-    <t>./config/bms/BCU_协能.xlsx</t>
+    <t>192.168.0.20</t>
+  </si>
+  <si>
+    <t>IEC104</t>
+  </si>
+  <si>
+    <t>./config/测控/测控柜_万润.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.111</t>
   </si>
   <si>
     <t>device_id</t>
@@ -545,7 +440,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,13 +452,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1133,137 +1021,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1280,12 +1168,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1713,401 +1595,401 @@
     <col min="8" max="16384" width="9.03100775193798" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" spans="1:7">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="6" customFormat="1" spans="1:7">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" s="9" customFormat="1" spans="1:7">
-      <c r="A2" s="9" t="s">
+    <row r="2" s="7" customFormat="1" spans="1:7">
+      <c r="A2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="9" t="b">
+      <c r="F2" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="10" customFormat="1" spans="1:7">
-      <c r="A3" s="10" t="s">
+    <row r="3" s="8" customFormat="1" spans="1:7">
+      <c r="A3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="10" t="b">
+      <c r="F3" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" s="10" customFormat="1" spans="1:7">
-      <c r="B4" s="10" t="s">
+    <row r="4" s="8" customFormat="1" spans="1:7">
+      <c r="B4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="8">
         <v>9091</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" s="11" customFormat="1" spans="1:7">
-      <c r="A5" s="11" t="s">
+    <row r="5" s="9" customFormat="1" spans="1:7">
+      <c r="A5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="11" t="b">
+      <c r="F5" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" s="12" customFormat="1" spans="1:7">
-      <c r="A6" s="12" t="s">
+    <row r="6" s="10" customFormat="1" spans="1:7">
+      <c r="A6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="12" t="b">
+      <c r="F6" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" s="12" customFormat="1" spans="1:7">
-      <c r="B7" s="12" t="s">
+    <row r="7" s="10" customFormat="1" spans="1:7">
+      <c r="B7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="10">
         <v>9092</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" s="12" customFormat="1" spans="1:7">
-      <c r="B8" s="12" t="s">
+    <row r="8" s="10" customFormat="1" spans="1:7">
+      <c r="B8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" s="13" customFormat="1" spans="1:7">
-      <c r="A9" s="13" t="s">
+    <row r="9" s="11" customFormat="1" spans="1:7">
+      <c r="A9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="17" t="b">
+      <c r="F9" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" s="13" customFormat="1" spans="1:7">
-      <c r="B10" s="13" t="s">
+    <row r="10" s="11" customFormat="1" spans="1:7">
+      <c r="B10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>2404</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" s="13" customFormat="1" spans="1:7">
-      <c r="B11" s="13" t="s">
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+    </row>
+    <row r="11" s="11" customFormat="1" spans="1:7">
+      <c r="B11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" s="13" customFormat="1" spans="1:7">
-      <c r="B12" s="13" t="s">
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+    </row>
+    <row r="12" s="11" customFormat="1" spans="1:7">
+      <c r="B12" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="11">
         <v>0</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" s="13" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B13" s="13" t="s">
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" s="11" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B13" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="13" t="b">
+      <c r="C13" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" s="13" customFormat="1" spans="1:7">
-      <c r="B14" s="13" t="s">
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+    </row>
+    <row r="14" s="11" customFormat="1" spans="1:7">
+      <c r="B14" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="11">
         <v>30000</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" s="13" customFormat="1" ht="36.85" spans="1:7">
-      <c r="B15" s="13" t="s">
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+    </row>
+    <row r="15" s="11" customFormat="1" ht="36.85" spans="1:7">
+      <c r="B15" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="13" t="b">
+      <c r="C15" s="11" t="b">
         <v>0</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-    </row>
-    <row r="16" s="14" customFormat="1" spans="1:7">
-      <c r="A16" s="21" t="s">
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" s="12" customFormat="1" spans="1:7">
+      <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="22" t="b">
+      <c r="F16" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" s="14" customFormat="1" spans="1:7">
-      <c r="A17" s="22"/>
-      <c r="B17" s="14" t="s">
+    <row r="17" s="12" customFormat="1" spans="1:7">
+      <c r="A17" s="20"/>
+      <c r="B17" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="12">
         <v>500</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-    </row>
-    <row r="18" s="14" customFormat="1" spans="1:7">
-      <c r="A18" s="22"/>
-      <c r="B18" s="14" t="s">
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" s="12" customFormat="1" spans="1:7">
+      <c r="A18" s="20"/>
+      <c r="B18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="12">
         <v>60000</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-    </row>
-    <row r="19" s="14" customFormat="1" spans="1:7">
-      <c r="A19" s="22"/>
-      <c r="B19" s="14" t="s">
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" s="12" customFormat="1" spans="1:7">
+      <c r="A19" s="20"/>
+      <c r="B19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="12">
         <v>1</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-    </row>
-    <row r="20" s="14" customFormat="1" spans="1:7">
-      <c r="A20" s="22"/>
-      <c r="B20" s="14" t="s">
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" s="12" customFormat="1" spans="1:7">
+      <c r="A20" s="20"/>
+      <c r="B20" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="12">
         <v>1</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-    </row>
-    <row r="21" s="14" customFormat="1" ht="36.85" spans="1:7">
-      <c r="A21" s="22"/>
-      <c r="B21" s="14" t="s">
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" s="12" customFormat="1" ht="36.85" spans="1:7">
+      <c r="A21" s="20"/>
+      <c r="B21" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C21" s="23" t="b">
+      <c r="C21" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-    </row>
-    <row r="22" s="15" customFormat="1" spans="1:7">
-      <c r="A22" s="15" t="s">
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" s="13" customFormat="1" spans="1:7">
+      <c r="A22" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="15" t="b">
+      <c r="F22" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="15" t="s">
+      <c r="G22" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="23" s="16" customFormat="1" spans="1:7">
-      <c r="A23" s="16" t="s">
+    <row r="23" s="14" customFormat="1" spans="1:7">
+      <c r="A23" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="F23" s="16" t="b">
+      <c r="F23" s="14" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="14" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="24" s="16" customFormat="1" spans="1:7">
-      <c r="B24" s="16" t="s">
+    <row r="24" s="14" customFormat="1" spans="1:7">
+      <c r="B24" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="14">
         <v>1883</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" s="16" customFormat="1" spans="1:7">
-      <c r="B25" s="16" t="s">
+    <row r="25" s="14" customFormat="1" spans="1:7">
+      <c r="B25" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" s="16" customFormat="1" spans="1:7">
-      <c r="B26" s="16" t="s">
+    <row r="26" s="14" customFormat="1" spans="1:7">
+      <c r="B26" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="14" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="27" s="16" customFormat="1" spans="1:7">
-      <c r="B27" s="16" t="s">
+    <row r="27" s="14" customFormat="1" spans="1:7">
+      <c r="B27" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="28" s="16" customFormat="1" spans="1:7">
-      <c r="B28" s="16" t="s">
+    <row r="28" s="14" customFormat="1" spans="1:7">
+      <c r="B28" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="14" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2249,8 +2131,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelCol="4"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelRow="2" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.45736434108527" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.9302325581395" style="2" customWidth="1"/>
@@ -2302,412 +2184,6 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="2">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="2">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="2">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="2">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="2">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="2">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="2">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="2">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="2">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="2">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="2">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="2">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2">
-        <v>29</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="2">
-        <v>30</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="2">
-        <v>31</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2718,8 +2194,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4"/>
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="6.45736434108527" style="5" customWidth="1"/>
     <col min="2" max="2" width="15.5968992248062" style="5" customWidth="1"/>
@@ -2745,16 +2221,16 @@
         <v>101</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>17</v>
@@ -2763,51 +2239,51 @@
         <v>21</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="Q1" s="4" t="s">
         <v>102</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="1" spans="1:19">
-      <c r="A2" s="5">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>104</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="F2" s="5">
         <v>2000</v>
@@ -2816,7 +2292,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="I2" s="5">
         <v>502</v>
@@ -2835,420 +2311,33 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" spans="1:19">
-      <c r="A3" s="5">
+    <row r="3" spans="1:19">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>157</v>
+      <c r="D3" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="F3" s="5">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="G3" s="5">
         <v>2000</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="I3" s="5">
-        <v>502</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" s="5" customFormat="1" spans="1:19">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G4" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" s="5">
-        <v>502</v>
-      </c>
-      <c r="J4" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" s="5" customFormat="1" spans="1:19">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F5" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I5" s="5">
-        <v>502</v>
-      </c>
-      <c r="J5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" s="5" customFormat="1" spans="1:19">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I6" s="5">
-        <v>502</v>
-      </c>
-      <c r="J6" s="5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" s="5" customFormat="1" spans="1:19">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="5">
-        <v>502</v>
-      </c>
-      <c r="J7" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="1" spans="1:19">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G8" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I8" s="5">
-        <v>502</v>
-      </c>
-      <c r="J8" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" spans="1:19">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I9" s="5">
-        <v>502</v>
-      </c>
-      <c r="J9" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="1" spans="1:19">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F10" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="5">
-        <v>502</v>
-      </c>
-      <c r="J10" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" s="5" customFormat="1" spans="1:19">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G11" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I11" s="5">
-        <v>502</v>
-      </c>
-      <c r="J11" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" s="5" customFormat="1" spans="1:19">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F12" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G12" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I12" s="5">
-        <v>502</v>
-      </c>
-      <c r="J12" s="5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" s="5" customFormat="1" spans="1:19">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F13" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G13" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I13" s="5">
-        <v>502</v>
-      </c>
-      <c r="J13" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" s="5" customFormat="1" spans="1:19">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F14" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G14" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I14" s="5">
-        <v>502</v>
-      </c>
-      <c r="J14" s="5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" s="5" customFormat="1" spans="1:19">
-      <c r="A15" s="5">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F15" s="5">
-        <v>2000</v>
-      </c>
-      <c r="G15" s="5">
-        <v>2000</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="I15" s="5">
-        <v>502</v>
-      </c>
-      <c r="J15" s="5">
-        <v>13</v>
+        <v>2404</v>
       </c>
     </row>
   </sheetData>
@@ -3275,13 +2364,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>
